--- a/ig/main/ValueSet-JDV-J60-FormatCode-DMP.xlsx
+++ b/ig/main/ValueSet-JDV-J60-FormatCode-DMP.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240927120000</t>
+    <t>20260928120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-27T12:00:00+01:00</t>
+    <t>2026-09-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -471,10 +471,10 @@
     <t>1.2.840.10008.5.1.4.1.1.88.59</t>
   </si>
   <si>
-    <t>Document Références d'objets d'un examen d'imagerie selon profil IHE RAD XDS-I</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_A09-DICOMuidRegistry/FHIR/TRE-A09-DICOMuidRegistry</t>
+    <t>Key Object Selection Document Storage</t>
+  </si>
+  <si>
+    <t>http://dicom.nema.org/resources/ontology/DCMUID</t>
   </si>
   <si>
     <t>http://www.w3.org/2000/09/xmldsig#</t>
